--- a/StructureDefinition-inera-ehds-patient.xlsx
+++ b/StructureDefinition-inera-ehds-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>genderIdentity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-genderIdentity|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {individual-genderIdentity|5.3.0}
 </t>
   </si>
   <si>
@@ -485,7 +485,7 @@
     <t>personalPronouns</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-pronouns|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {individual-pronouns|5.3.0}
 </t>
   </si>
   <si>

--- a/StructureDefinition-inera-ehds-patient.xlsx
+++ b/StructureDefinition-inera-ehds-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-patient.xlsx
+++ b/StructureDefinition-inera-ehds-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-patient.xlsx
+++ b/StructureDefinition-inera-ehds-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>genderIdentity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-genderIdentity|5.3.0}
+    <t xml:space="preserve">Extension {individual-genderIdentity|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -485,7 +485,7 @@
     <t>personalPronouns</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-pronouns|5.3.0}
+    <t xml:space="preserve">Extension {individual-pronouns|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
